--- a/data/primary_school/data.xlsx
+++ b/data/primary_school/data.xlsx
@@ -1652,16 +1652,16 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>34.24180278</v>
+        <v>34.24322</v>
       </c>
       <c r="C49" t="str">
-        <v>134.00913944</v>
+        <v>134.00856</v>
       </c>
       <c r="D49" t="str">
         <v>高松市立香南小学校</v>
       </c>
       <c r="E49" t="str">
-        <v>高松市香南町横井1008</v>
+        <v>高松市香南町横井801</v>
       </c>
       <c r="F49" t="str">
         <v>087-879-2269</v>
@@ -1795,6 +1795,12 @@
       </c>
       <c r="F54" t="str">
         <v>087-881-6310</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
